--- a/01_Input/00_CO Validation/Cuba - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Cuba - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27018"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="110" documentId="11_8CC573B517C32C88C802DE539ED75CBA98A8355C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB9D4FF6-8C48-42BC-99C8-28DA8B6C06A4}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="11_8CC573B517C32C88C802DE539ED75CBA98A8355C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B66BBD97-89A6-4B11-8B2B-1F500FB4F7E0}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,6 +15,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="94">
   <si>
     <t>Project ID</t>
   </si>
@@ -139,6 +142,166 @@
     <t>http://open.undp.org/projects/00110578</t>
   </si>
   <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">A generation capacity of 1,654.6 MW was installed through photovoltaic energy in 818 local communities (827 SPVs installed and 2000 SPVs repaired). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> This indicator has been included in the fourth Situation Report to the European Union.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Note - this output has been reduced to 100 to provide a more realistic estimate, TBD to confirm with country office</t>
+    </r>
+  </si>
+  <si>
+    <t>MUNICIPIO MARTI ENERGIA SOSTENIBLE</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00118945</t>
+  </si>
+  <si>
+    <t>Number of direct beneficiaries of the project by use of biomethane public transport</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Five low-emission public transport buses will be put into operation in the Martí Municipality, after the installation of a biomethane plant with its filling stations. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> This indicator will be declared in a future Situationt Report to the European Union, once the technology will be installed.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cuba Sustainable Transport</t>
+  </si>
+  <si>
+    <t>PIMS+</t>
+  </si>
+  <si>
+    <t>Number of direct beneficiaries of the project by the Transit Oriented Development (TOD) measures and NMT.</t>
+  </si>
+  <si>
+    <t>Pilot intervention on Sustainable Transport  Mobility (electric tricycles) was implemented in the Havana city.</t>
+  </si>
+  <si>
+    <t>CleanEnerg Cuba</t>
+  </si>
+  <si>
+    <t>Clean Cooking</t>
+  </si>
+  <si>
+    <t>Number of people directly and indirectly benefited from  renewable energy due to project action.</t>
+  </si>
+  <si>
+    <t>Pilot intervention on biogas and biodiesel to promote the use of bioenergy technologies by rural farmers.</t>
+  </si>
+  <si>
+    <t>Accelerating just energy transition</t>
+  </si>
+  <si>
+    <t>Apoyo a la revitalización del empleo en la cadena de producción ganadera de la provincia de Guantánamo, en la etapa de Recuperación post COVID-19</t>
+  </si>
+  <si>
+    <t>Empleo Autoabastecimiento COVID-19 | UNDP Transparency Portal</t>
+  </si>
+  <si>
+    <t>Agricultural Services</t>
+  </si>
+  <si>
+    <t>Number of direct beneficiaries of the project by the renewable energy solutions (irrigation: photovoltaic) installed in family farms.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pilot intervention on renewable energy solutions (irrigation: photovoltaic) was implemented to support 16 family farms in Guantánamo province. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> This indicator will be declared in a future Implementation Report to the TFD Russia-UNDP, once the technology will be installed.</t>
+    </r>
+  </si>
+  <si>
+    <t>ALASS</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00118495</t>
+  </si>
+  <si>
+    <t>Number of direct beneficiaries of the project by the renewable energy solutions installed to support the local agri-food systems.</t>
+  </si>
+  <si>
+    <t>Pilot interventions on renewable energy solutions (irrigation: photovoltaic; biogas: mini-industries, windmills for water supply )  will be implemented to support the sustainability of local agri-food systems in 16 selected communities.</t>
+  </si>
+  <si>
+    <t>Agrofrutales</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00085124</t>
+  </si>
+  <si>
+    <t>Renewable energy solutions for fruit production (irrigation: photovoltaic)  will be implemented in selected farms.</t>
+  </si>
+  <si>
     <t>Numberphotovoltaic systems (PVSs) installed or repaired.</t>
   </si>
   <si>
@@ -166,21 +329,6 @@
     </r>
   </si>
   <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
-    <t>MW</t>
-  </si>
-  <si>
-    <t>MUNICIPIO MARTI ENERGIA SOSTENIBLE</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00118945</t>
-  </si>
-  <si>
-    <t>Number of direct beneficiaries of the project by use of biomethane public transport</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Five low-emission public transport buses will be put into operation in the Martí Municipality, after the installation of a biomethane plant with its filling stations. </t>
     </r>
@@ -203,88 +351,6 @@
     </r>
   </si>
   <si>
-    <t>Cuba Sustainable Transport</t>
-  </si>
-  <si>
-    <t>PIMS+</t>
-  </si>
-  <si>
-    <t>Number of direct beneficiaries of the project by the Transit Oriented Development (TOD) measures and NMT.</t>
-  </si>
-  <si>
-    <t>Pilot intervention on Sustainable Transport  Mobility (electric tricycles) was implemented in the Havana city.</t>
-  </si>
-  <si>
-    <t>CleanEnerg Cuba</t>
-  </si>
-  <si>
-    <t>Clean Cooking</t>
-  </si>
-  <si>
-    <t>Number of people directly and indirectly benefited from  renewable energy due to project action.</t>
-  </si>
-  <si>
-    <t>Pilot intervention on biogas and biodiesel to promote the use of bioenergy technologies by rural farmers.</t>
-  </si>
-  <si>
-    <t>Accelerating just energy transition</t>
-  </si>
-  <si>
-    <t>Apoyo a la revitalización del empleo en la cadena de producción ganadera de la provincia de Guantánamo, en la etapa de Recuperación post COVID-19</t>
-  </si>
-  <si>
-    <t>Empleo Autoabastecimiento COVID-19 | UNDP Transparency Portal</t>
-  </si>
-  <si>
-    <t>Agricultural Services</t>
-  </si>
-  <si>
-    <t>Number of direct beneficiaries of the project by the renewable energy solutions (irrigation: photovoltaic) installed in family farms.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Pilot intervention on renewable energy solutions (irrigation: photovoltaic) was implemented to support 16 family farms in Guantánamo province. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Note:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> This indicator will be declared in a future Implementation Report to the TFD Russia-UNDP, once the technology will be installed.</t>
-    </r>
-  </si>
-  <si>
-    <t>ALASS</t>
-  </si>
-  <si>
-    <t>https://open.undp.org/projects/00118495</t>
-  </si>
-  <si>
-    <t>Number of direct beneficiaries of the project by the renewable energy solutions installed to support the local agri-food systems.</t>
-  </si>
-  <si>
-    <t>Pilot interventions on renewable energy solutions (irrigation: photovoltaic; biogas: mini-industries, windmills for water supply )  will be implemented to support the sustainability of local agri-food systems in 16 selected communities.</t>
-  </si>
-  <si>
-    <t>Agrofrutales</t>
-  </si>
-  <si>
-    <t>https://open.undp.org/projects/00085124</t>
-  </si>
-  <si>
-    <t>Renewable energy solutions for fruit production (irrigation: photovoltaic)  will be implemented in selected farms.</t>
-  </si>
-  <si>
     <t>2, 451</t>
   </si>
   <si>
@@ -394,11 +460,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,8 +525,30 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -511,6 +600,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,6 +741,57 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -670,64 +816,13 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1035,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662F1B48-A46B-4040-AF4E-9FDFB8BEACA0}">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="3" width="20.7109375" customWidth="1"/>
@@ -1043,6 +1138,7 @@
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="8" width="12.7109375" customWidth="1"/>
     <col min="9" max="9" width="32.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
     <col min="13" max="13" width="48.5703125" customWidth="1"/>
     <col min="15" max="15" width="11.5703125" customWidth="1"/>
     <col min="16" max="16" width="12.7109375" customWidth="1"/>
@@ -1050,441 +1146,419 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="45.75">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="M1" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="39" t="s">
+      <c r="O1" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="39" t="s">
+      <c r="P1" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="39" t="s">
+      <c r="Q1" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="39" t="s">
+      <c r="R1" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="39" t="s">
+      <c r="S1" s="36" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="26" customFormat="1" ht="183">
-      <c r="A2" s="40">
+    <row r="2" spans="1:19" ht="183">
+      <c r="A2" s="37">
         <v>98897</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="52">
+      <c r="D2" s="38">
         <v>3578420</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="39">
         <v>0</v>
       </c>
-      <c r="H2" s="55">
+      <c r="H2" s="40">
         <v>2451</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40" t="s">
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-    </row>
-    <row r="3" spans="1:19" ht="121.5">
-      <c r="A3" s="44">
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+    </row>
+    <row r="3" spans="1:19" ht="198">
+      <c r="A3" s="31">
         <v>110578</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="53">
+      <c r="D3" s="33">
         <v>7710027</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46" t="s">
+      <c r="E3" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="46">
+      <c r="F3" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="34">
         <v>0</v>
       </c>
-      <c r="H3" s="56">
-        <v>2827</v>
-      </c>
-      <c r="I3" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-    </row>
-    <row r="4" spans="1:19" s="26" customFormat="1" ht="60.75">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="42" t="s">
+      <c r="H3" s="57">
+        <v>100</v>
+      </c>
+      <c r="I3" s="55" t="s">
         <v>30</v>
       </c>
+      <c r="J3" s="46">
+        <f>H3*17500</f>
+        <v>1750000</v>
+      </c>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+    </row>
+    <row r="4" spans="1:19" ht="137.25">
+      <c r="A4" s="37">
+        <v>118945</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="38">
+        <v>433162</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>21</v>
+      </c>
       <c r="F4" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="42"/>
-      <c r="H4" s="55">
-        <v>1654.6</v>
-      </c>
-      <c r="I4" s="42"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="42">
+        <v>0</v>
+      </c>
+      <c r="H4" s="43">
+        <v>22000</v>
+      </c>
+      <c r="I4" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+    </row>
+    <row r="5" spans="1:19" ht="91.5">
+      <c r="A5" s="37">
+        <v>5653</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="38">
+        <v>1959132</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="39">
+        <v>0</v>
+      </c>
+      <c r="H5" s="40">
+        <v>132820</v>
+      </c>
+      <c r="I5" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+    </row>
+    <row r="6" spans="1:19" ht="76.5">
+      <c r="A6" s="37">
+        <v>4899</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="38">
+        <v>2737524</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="39">
+        <v>0</v>
+      </c>
+      <c r="H6" s="40">
+        <v>88100</v>
+      </c>
+      <c r="I6" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="O6" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37"/>
+      <c r="S6" s="37"/>
+    </row>
+    <row r="7" spans="1:19" ht="137.25">
+      <c r="A7" s="42">
+        <v>120932</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="38">
+        <v>100000</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="42">
+        <v>0</v>
+      </c>
+      <c r="H7" s="43">
+        <v>64</v>
+      </c>
+      <c r="I7" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="P4" s="40" t="s">
+      <c r="P7" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-    </row>
-    <row r="5" spans="1:19" ht="137.25">
-      <c r="A5" s="44">
-        <v>118945</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="53">
-        <v>433162</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="47">
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
+    </row>
+    <row r="8" spans="1:19" ht="121.5">
+      <c r="A8" s="37">
+        <v>118495</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="38">
+        <v>800000</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="42">
         <v>0</v>
       </c>
-      <c r="H5" s="57">
-        <v>22000</v>
-      </c>
-      <c r="I5" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-    </row>
-    <row r="6" spans="1:19" ht="91.5">
-      <c r="A6" s="44">
-        <v>5653</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="53">
-        <v>1959132</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="46">
+      <c r="H8" s="43">
+        <v>100000</v>
+      </c>
+      <c r="I8" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="37"/>
+    </row>
+    <row r="9" spans="1:19" ht="106.5">
+      <c r="A9" s="39">
+        <v>85124</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="45">
+        <v>128000</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="42">
         <v>0</v>
       </c>
-      <c r="H6" s="56">
-        <v>132820</v>
-      </c>
-      <c r="I6" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-    </row>
-    <row r="7" spans="1:19" ht="76.5">
-      <c r="A7" s="44">
-        <v>4899</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="53">
-        <v>2737524</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="46">
-        <v>0</v>
-      </c>
-      <c r="H7" s="56">
-        <v>88100</v>
-      </c>
-      <c r="I7" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="P7" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-    </row>
-    <row r="8" spans="1:19" ht="137.25">
-      <c r="A8" s="48">
-        <v>120932</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="53">
-        <v>100000</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="47">
-        <v>0</v>
-      </c>
-      <c r="H8" s="57">
-        <v>64</v>
-      </c>
-      <c r="I8" s="47" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="P8" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-    </row>
-    <row r="9" spans="1:19" ht="121.5">
-      <c r="A9" s="44">
-        <v>118495</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="53">
-        <v>800000</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="47">
-        <v>0</v>
-      </c>
-      <c r="H9" s="57">
-        <v>100000</v>
-      </c>
-      <c r="I9" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-    </row>
-    <row r="10" spans="1:19" ht="106.5">
-      <c r="A10" s="49">
-        <v>85124</v>
-      </c>
-      <c r="B10" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="51" t="s">
+      <c r="H9" s="43">
+        <v>10</v>
+      </c>
+      <c r="I9" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="54">
-        <v>128000</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="47">
-        <v>0</v>
-      </c>
-      <c r="H10" s="57">
-        <v>10</v>
-      </c>
-      <c r="I10" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S10" xr:uid="{876AEDA9-B2BE-4622-ADDF-52E4A1AA5F7B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P4:P9 P2:P3" xr:uid="{3709A748-5F07-400A-8878-D6DCA1FDC763}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4:O9 O2:O3" xr:uid="{4A398C99-E181-4FEC-9970-D44305110068}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S9" xr:uid="{876AEDA9-B2BE-4622-ADDF-52E4A1AA5F7B}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R10" xr:uid="{46CA21C1-C776-43C8-962E-F9AEF7884DC3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R9" xr:uid="{46CA21C1-C776-43C8-962E-F9AEF7884DC3}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q10" xr:uid="{83222196-6AD0-41C9-A681-F02CD81BDE15}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q9" xr:uid="{83222196-6AD0-41C9-A681-F02CD81BDE15}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P10" xr:uid="{3709A748-5F07-400A-8878-D6DCA1FDC763}">
-      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O10" xr:uid="{4A398C99-E181-4FEC-9970-D44305110068}">
-      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{E5D8FF80-2673-43D2-97E6-D2664D80DD3D}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{4B863770-AF04-4696-A411-D86B3CCD7D4C}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{D036BA61-C562-4651-9C40-05BB629E8AF2}"/>
-    <hyperlink ref="C8" r:id="rId4" xr:uid="{4125A59E-1D43-4E3A-87EC-EDD48F919EBE}"/>
-    <hyperlink ref="C9" r:id="rId5" xr:uid="{D304957A-E5F7-4794-8072-FC4FDC524C8E}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{D036BA61-C562-4651-9C40-05BB629E8AF2}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{4125A59E-1D43-4E3A-87EC-EDD48F919EBE}"/>
+    <hyperlink ref="C8" r:id="rId5" xr:uid="{D304957A-E5F7-4794-8072-FC4FDC524C8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1494,7 +1568,7 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E11:E17</xm:sqref>
+          <xm:sqref>E10:E16</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1610,21 +1684,21 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="121.5">
-      <c r="A3" s="30">
+      <c r="A3" s="47">
         <v>110578</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="47">
         <v>7710027</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="9" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="G3" s="8">
         <v>0</v>
@@ -1633,7 +1707,7 @@
         <v>2827</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -1646,15 +1720,15 @@
       <c r="S3" s="26"/>
     </row>
     <row r="4" spans="1:19" s="26" customFormat="1">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="31"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="48"/>
       <c r="E4" s="22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G4" s="22"/>
       <c r="H4" s="22">
@@ -1677,10 +1751,10 @@
         <v>118945</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="D5" s="5">
         <v>433162</v>
@@ -1689,7 +1763,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" s="13">
         <v>0</v>
@@ -1698,7 +1772,7 @@
         <v>22000</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -1715,10 +1789,10 @@
         <v>5653</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="D6" s="5">
         <v>1959132</v>
@@ -1727,7 +1801,7 @@
         <v>21</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" s="8">
         <v>0</v>
@@ -1736,7 +1810,7 @@
         <v>132820</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -1753,19 +1827,19 @@
         <v>4899</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="5">
         <v>2737524</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>42</v>
       </c>
       <c r="G7" s="8">
         <v>0</v>
@@ -1774,17 +1848,17 @@
         <v>88100</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="O7" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P7" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="26"/>
       <c r="R7" s="26"/>
@@ -1795,19 +1869,19 @@
         <v>120932</v>
       </c>
       <c r="B8" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>45</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>46</v>
       </c>
       <c r="D8" s="5">
         <v>100000</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>48</v>
       </c>
       <c r="G8" s="13">
         <v>0</v>
@@ -1816,7 +1890,7 @@
         <v>64</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1837,19 +1911,19 @@
         <v>118495</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="D9" s="5">
         <v>800000</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="13">
         <v>0</v>
@@ -1858,7 +1932,7 @@
         <v>100000</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1875,19 +1949,19 @@
         <v>85124</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>54</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>55</v>
       </c>
       <c r="D10" s="19">
         <v>128000</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
@@ -1896,7 +1970,7 @@
         <v>10</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -2021,7 +2095,7 @@
         <v>3578420</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>22</v>
@@ -2030,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>23</v>
@@ -2054,10 +2128,10 @@
         <v>7710027</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G3" s="8">
         <v>0</v>
@@ -2066,7 +2140,7 @@
         <v>2827</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -2078,10 +2152,10 @@
         <v>118945</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="5">
         <v>433162</v>
@@ -2090,7 +2164,7 @@
         <v>21</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4" s="13">
         <v>0</v>
@@ -2099,7 +2173,7 @@
         <v>22000</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -2111,10 +2185,10 @@
         <v>5653</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="D5" s="5">
         <v>1959132</v>
@@ -2123,7 +2197,7 @@
         <v>21</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" s="8">
         <v>0</v>
@@ -2132,7 +2206,7 @@
         <v>132820</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -2144,19 +2218,19 @@
         <v>4899</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="5">
         <v>2737524</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>42</v>
       </c>
       <c r="G6" s="8">
         <v>0</v>
@@ -2165,7 +2239,7 @@
         <v>88100</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -2177,19 +2251,19 @@
         <v>120932</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>45</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>46</v>
       </c>
       <c r="D7" s="5">
         <v>100000</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>48</v>
       </c>
       <c r="G7" s="13">
         <v>0</v>
@@ -2198,7 +2272,7 @@
         <v>64</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -2210,19 +2284,19 @@
         <v>118495</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="D8" s="5">
         <v>800000</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" s="13">
         <v>0</v>
@@ -2231,7 +2305,7 @@
         <v>100000</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -2243,19 +2317,19 @@
         <v>85124</v>
       </c>
       <c r="B9" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>54</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>55</v>
       </c>
       <c r="D9" s="19">
         <v>128000</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="13">
         <v>0</v>
@@ -2264,7 +2338,7 @@
         <v>10</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -2305,160 +2379,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="34" t="s">
-        <v>61</v>
+      <c r="A2" s="51" t="s">
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="34"/>
+      <c r="A3" s="51"/>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="34"/>
+      <c r="A4" s="51"/>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="35" t="s">
-        <v>66</v>
+      <c r="A5" s="52" t="s">
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="35"/>
+      <c r="A6" s="52"/>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="35"/>
+      <c r="A7" s="52"/>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="35"/>
+      <c r="A8" s="52"/>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="35"/>
+      <c r="A9" s="52"/>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="36" t="s">
-        <v>75</v>
+      <c r="A10" s="53" t="s">
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="36"/>
+      <c r="A11" s="53"/>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="37" t="s">
-        <v>80</v>
+      <c r="A12" s="54" t="s">
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="54"/>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="37"/>
+      <c r="A14" s="54"/>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2473,6 +2547,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2721,28 +2815,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{494C9A6E-DB60-4C5B-A591-DCCAD84DBDB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23A76618-C921-44CE-8B1C-597576FB1E58}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2750,5 +2824,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23A76618-C921-44CE-8B1C-597576FB1E58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{494C9A6E-DB60-4C5B-A591-DCCAD84DBDB3}"/>
 </file>
--- a/01_Input/00_CO Validation/Cuba - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Cuba - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27221"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29325"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="181" documentId="11_8CC573B517C32C88C802DE539ED75CBA98A8355C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62F0D53D-D0F1-455C-BCF2-4F4EF5CABD45}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="11_8CC573B517C32C88C802DE539ED75CBA98A8355C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06FCC8B1-50F4-4A85-B1FF-9DD38831ED2F}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="112">
   <si>
     <t>Project ID</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>Policy Population</t>
+  </si>
+  <si>
+    <t>Project doc</t>
   </si>
   <si>
     <t>FRELOCAL - FUENTES RENOVABLES DE ENERGIA - DES LOCAL</t>
@@ -204,6 +207,9 @@
     <t>Accelerating just energy transition</t>
   </si>
   <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>MUNICIPIO MARTI ENERGIA SOSTENIBLE</t>
   </si>
   <si>
@@ -246,7 +252,7 @@
     <t>Cuba Sustainable Transport</t>
   </si>
   <si>
-    <t>PIMS+</t>
+    <t>https://co.pims.undp.org/project/view?id=5653</t>
   </si>
   <si>
     <t>Number of direct beneficiaries of the project by the Transit Oriented Development (TOD) measures and NMT.</t>
@@ -255,10 +261,16 @@
     <t>Pilot intervention on Sustainable Transport  Mobility (electric tricycles) was implemented in the Havana city.</t>
   </si>
   <si>
+    <t>GEF</t>
+  </si>
+  <si>
     <t>VF</t>
   </si>
   <si>
     <t>CleanEnerg Cuba</t>
+  </si>
+  <si>
+    <t>https://co.pims.undp.org/project/view?id=4899</t>
   </si>
   <si>
     <t>Clean Cooking</t>
@@ -392,6 +404,9 @@
     </r>
   </si>
   <si>
+    <t>PIMS+</t>
+  </si>
+  <si>
     <t>Agricultural Services</t>
   </si>
   <si>
@@ -515,7 +530,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -605,6 +620,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -714,19 +737,16 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -746,7 +766,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -767,15 +787,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -847,26 +867,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1173,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662F1B48-A46B-4040-AF4E-9FDFB8BEACA0}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="3" width="20.7109375" customWidth="1"/>
@@ -1192,9 +1222,10 @@
     <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="45.75">
+    <row r="1" spans="1:22" ht="45.75">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
@@ -1258,25 +1289,28 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" ht="183">
+      <c r="V1" s="56" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="183">
       <c r="A2" s="34">
         <v>98897</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="35">
         <v>3578420</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="36">
         <v>0</v>
@@ -1285,45 +1319,45 @@
         <v>2451</v>
       </c>
       <c r="I2" s="36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="34"/>
       <c r="K2" s="34"/>
       <c r="L2" s="50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="46"/>
       <c r="N2" s="51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O2" s="46"/>
       <c r="P2" s="46"/>
       <c r="Q2" s="46"/>
       <c r="R2" s="46"/>
       <c r="S2" s="52" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T2" s="50"/>
       <c r="U2" s="52"/>
     </row>
-    <row r="3" spans="1:21" ht="305.25">
+    <row r="3" spans="1:22" ht="305.25">
       <c r="A3" s="28">
         <v>110578</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="30">
         <v>7710027</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="31">
         <v>0</v>
@@ -1332,45 +1366,48 @@
         <v>6407</v>
       </c>
       <c r="I3" s="43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3" s="42"/>
       <c r="K3" s="28"/>
       <c r="L3" s="50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" s="46"/>
       <c r="N3" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="46"/>
       <c r="P3" s="46"/>
       <c r="Q3" s="46"/>
       <c r="R3" s="46"/>
       <c r="S3" s="52" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T3" s="50"/>
       <c r="U3" s="52"/>
-    </row>
-    <row r="4" spans="1:21" ht="137.25">
+      <c r="V3" s="56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="137.25">
       <c r="A4" s="34">
         <v>118945</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="35">
         <v>433162</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4" s="38">
         <v>0</v>
@@ -1379,16 +1416,16 @@
         <v>22000</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J4" s="34"/>
       <c r="K4" s="34"/>
       <c r="L4" s="50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M4" s="46"/>
       <c r="N4" s="51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O4" s="46"/>
       <c r="P4" s="46"/>
@@ -1397,25 +1434,28 @@
       <c r="S4" s="52"/>
       <c r="T4" s="50"/>
       <c r="U4" s="52"/>
-    </row>
-    <row r="5" spans="1:21" ht="91.5">
+      <c r="V4" s="56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="91.5">
       <c r="A5" s="34">
         <v>5653</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>42</v>
       </c>
       <c r="D5" s="35">
         <v>1959132</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G5" s="36">
         <v>0</v>
@@ -1424,16 +1464,18 @@
         <v>132820</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="34"/>
+        <v>44</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>45</v>
+      </c>
       <c r="K5" s="34"/>
       <c r="L5" s="50" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M5" s="46"/>
       <c r="N5" s="51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O5" s="46"/>
       <c r="P5" s="46"/>
@@ -1442,25 +1484,28 @@
       <c r="S5" s="52"/>
       <c r="T5" s="50"/>
       <c r="U5" s="52"/>
-    </row>
-    <row r="6" spans="1:21" ht="76.5">
+      <c r="V5" s="56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="76.5">
       <c r="A6" s="34">
         <v>4899</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>40</v>
+        <v>47</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>48</v>
       </c>
       <c r="D6" s="35">
         <v>2737524</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G6" s="36">
         <v>0</v>
@@ -1469,16 +1514,18 @@
         <v>88100</v>
       </c>
       <c r="I6" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="34"/>
+        <v>51</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>45</v>
+      </c>
       <c r="K6" s="34"/>
       <c r="L6" s="50" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M6" s="46"/>
       <c r="N6" s="51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O6" s="46"/>
       <c r="P6" s="46"/>
@@ -1487,25 +1534,28 @@
       <c r="S6" s="52"/>
       <c r="T6" s="50"/>
       <c r="U6" s="52"/>
-    </row>
-    <row r="7" spans="1:21" ht="137.25">
+      <c r="V6" s="56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="137.25">
       <c r="A7" s="38">
         <v>120932</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D7" s="35">
         <v>100000</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G7" s="38">
         <v>0</v>
@@ -1514,16 +1564,16 @@
         <v>64</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J7" s="34"/>
       <c r="K7" s="34"/>
       <c r="L7" s="50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7" s="46"/>
       <c r="N7" s="51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O7" s="46"/>
       <c r="P7" s="46"/>
@@ -1533,24 +1583,24 @@
       <c r="T7" s="50"/>
       <c r="U7" s="52"/>
     </row>
-    <row r="8" spans="1:21" ht="121.5">
+    <row r="8" spans="1:22" ht="121.5">
       <c r="A8" s="34">
         <v>118495</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>58</v>
       </c>
       <c r="D8" s="35">
         <v>800000</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8" s="38">
         <v>0</v>
@@ -1559,16 +1609,16 @@
         <v>100000</v>
       </c>
       <c r="I8" s="38" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J8" s="34"/>
       <c r="K8" s="34"/>
       <c r="L8" s="50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M8" s="46"/>
       <c r="N8" s="51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O8" s="46"/>
       <c r="P8" s="46"/>
@@ -1577,25 +1627,28 @@
       <c r="S8" s="52"/>
       <c r="T8" s="50"/>
       <c r="U8" s="52"/>
-    </row>
-    <row r="9" spans="1:21" ht="106.5">
+      <c r="V8" s="56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="106.5">
       <c r="A9" s="36">
         <v>85124</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D9" s="41">
         <v>128000</v>
       </c>
       <c r="E9" s="36" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9" s="38">
         <v>0</v>
@@ -1604,16 +1657,16 @@
         <v>10</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J9" s="34"/>
       <c r="K9" s="34"/>
       <c r="L9" s="50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M9" s="46"/>
       <c r="N9" s="51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O9" s="46"/>
       <c r="P9" s="46"/>
@@ -1659,6 +1712,8 @@
     <hyperlink ref="C4" r:id="rId3" xr:uid="{D036BA61-C562-4651-9C40-05BB629E8AF2}"/>
     <hyperlink ref="C7" r:id="rId4" xr:uid="{4125A59E-1D43-4E3A-87EC-EDD48F919EBE}"/>
     <hyperlink ref="C8" r:id="rId5" xr:uid="{D304957A-E5F7-4794-8072-FC4FDC524C8E}"/>
+    <hyperlink ref="C6" r:id="rId6" xr:uid="{087177D0-26E4-480D-ADFA-CA60FAFB2FF6}"/>
+    <hyperlink ref="C5" r:id="rId7" xr:uid="{21D15199-5395-4581-829A-33ECAF03C3E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1723,10 +1778,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="O1" s="26" t="s">
         <v>13</v>
@@ -1749,19 +1804,19 @@
         <v>98897</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="24">
         <v>3578420</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="19">
         <v>0</v>
@@ -1770,35 +1825,35 @@
         <v>2451</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="18"/>
       <c r="K2" s="18"/>
       <c r="L2" s="18"/>
       <c r="M2" s="22"/>
       <c r="O2" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P2" s="23" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="121.5">
-      <c r="A3" s="53">
+      <c r="A3" s="59">
         <v>110578</v>
       </c>
-      <c r="B3" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="55" t="s">
+      <c r="B3" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="53">
+      <c r="C3" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="59">
         <v>7710027</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -1807,7 +1862,7 @@
         <v>2827</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1820,15 +1875,15 @@
       <c r="S3" s="23"/>
     </row>
     <row r="4" spans="1:19" s="23" customFormat="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="54"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="60"/>
       <c r="E4" s="19" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G4" s="19"/>
       <c r="H4" s="19">
@@ -1840,10 +1895,10 @@
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="O4" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="137.25">
@@ -1851,19 +1906,19 @@
         <v>118945</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2">
         <v>433162</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G5" s="10">
         <v>0</v>
@@ -1872,7 +1927,7 @@
         <v>22000</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1889,19 +1944,19 @@
         <v>5653</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D6" s="2">
         <v>1959132</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -1910,7 +1965,7 @@
         <v>132820</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1927,19 +1982,19 @@
         <v>4899</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2">
         <v>2737524</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -1948,17 +2003,17 @@
         <v>88100</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="O7" s="23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P7" s="23" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="Q7" s="23"/>
       <c r="R7" s="23"/>
@@ -1969,19 +2024,19 @@
         <v>120932</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D8" s="2">
         <v>100000</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G8" s="10">
         <v>0</v>
@@ -1990,17 +2045,17 @@
         <v>64</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="O8" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q8" s="23"/>
       <c r="R8" s="23"/>
@@ -2011,19 +2066,19 @@
         <v>118495</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D9" s="2">
         <v>800000</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
@@ -2032,7 +2087,7 @@
         <v>100000</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2049,19 +2104,19 @@
         <v>85124</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D10" s="16">
         <v>128000</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G10" s="10">
         <v>0</v>
@@ -2070,7 +2125,7 @@
         <v>10</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -2175,10 +2230,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="183">
@@ -2186,28 +2241,28 @@
         <v>98897</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2">
         <v>3578420</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -2219,19 +2274,19 @@
         <v>110578</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2">
         <v>7710027</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -2240,7 +2295,7 @@
         <v>2827</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -2252,19 +2307,19 @@
         <v>118945</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2">
         <v>433162</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4" s="10">
         <v>0</v>
@@ -2273,7 +2328,7 @@
         <v>22000</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -2285,19 +2340,19 @@
         <v>5653</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D5" s="2">
         <v>1959132</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -2306,7 +2361,7 @@
         <v>132820</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -2318,19 +2373,19 @@
         <v>4899</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D6" s="2">
         <v>2737524</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -2339,7 +2394,7 @@
         <v>88100</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -2351,19 +2406,19 @@
         <v>120932</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2">
         <v>100000</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G7" s="10">
         <v>0</v>
@@ -2372,7 +2427,7 @@
         <v>64</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -2384,19 +2439,19 @@
         <v>118495</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2">
         <v>800000</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8" s="10">
         <v>0</v>
@@ -2405,7 +2460,7 @@
         <v>100000</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -2417,19 +2472,19 @@
         <v>85124</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D9" s="16">
         <v>128000</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
@@ -2438,7 +2493,7 @@
         <v>10</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2487,170 +2542,170 @@
     </row>
     <row r="2" spans="1:2" ht="45.75">
       <c r="A2" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="57" t="s">
-        <v>72</v>
+        <v>24</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>73</v>
+        <v>70</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
       <c r="A4" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="57" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
       <c r="A5" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
       <c r="A6" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="57" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
       <c r="A7" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="57" t="s">
-        <v>79</v>
+        <v>83</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
       <c r="A8" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="57" t="s">
-        <v>81</v>
+        <v>85</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
       <c r="A9" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="57" t="s">
-        <v>83</v>
+        <v>87</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
       <c r="A10" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="58" t="s">
-        <v>84</v>
+        <v>38</v>
+      </c>
+      <c r="B10" s="54" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
       <c r="A11" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
       <c r="A12" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>88</v>
+        <v>92</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
       <c r="A13" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="58" t="s">
-        <v>89</v>
+        <v>66</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="58" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
       <c r="A15" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>93</v>
+        <v>97</v>
+      </c>
+      <c r="B15" s="54" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
       <c r="A16" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" s="58" t="s">
-        <v>95</v>
+        <v>99</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
       <c r="A17" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="57" t="s">
-        <v>97</v>
+        <v>101</v>
+      </c>
+      <c r="B17" s="53" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
       <c r="A18" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" s="58" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+      <c r="B18" s="54" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
       <c r="A19" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="58" t="s">
-        <v>101</v>
+        <v>105</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
       <c r="A20" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="58" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
       <c r="A21" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="59" t="s">
-        <v>104</v>
+      <c r="B21" s="55" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
       <c r="A22" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="58" t="s">
-        <v>106</v>
+        <v>110</v>
+      </c>
+      <c r="B22" s="54" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2668,8 +2723,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55b7350c375998f6795677b1e38dfa8c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="12a65a177b511ef7abe69f5e8f04446c" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2694,6 +2760,8 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2773,6 +2841,16 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2916,25 +2994,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23A76618-C921-44CE-8B1C-597576FB1E58}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{494C9A6E-DB60-4C5B-A591-DCCAD84DBDB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BAF31EC-C830-485F-840F-98EEC1ACF5A1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BAF31EC-C830-485F-840F-98EEC1ACF5A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F912AB8C-74E4-40DB-AF13-972C3F1DBC8F}"/>
 </file>
--- a/01_Input/00_CO Validation/Cuba - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Cuba - Energy Projects.xlsx
@@ -260,7 +260,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -428,12 +428,12 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -443,16 +443,13 @@
     <xf numFmtId="165" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -549,6 +546,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K13" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L13" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K15" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L15" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K17" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L17" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1079,15 +1166,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K3" s="36" t="n">
+      <c r="K3" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="67" t="n"/>
-      <c r="M3" s="68" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L3" s="68" t="n"/>
+      <c r="M3" s="36" t="n"/>
       <c r="N3" s="34" t="n"/>
       <c r="O3" s="34" t="n"/>
       <c r="P3" s="46" t="n"/>
@@ -1194,15 +1277,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K5" s="31" t="n">
+      <c r="K5" s="67" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="71" t="n"/>
-      <c r="M5" s="72" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M5" s="43" t="n"/>
       <c r="N5" s="42" t="n"/>
       <c r="O5" s="28" t="n"/>
       <c r="P5" s="46" t="n"/>
@@ -1254,7 +1333,7 @@
       <c r="K6" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="73" t="n">
+      <c r="L6" s="72" t="n">
         <v>22000</v>
       </c>
       <c r="M6" s="44" t="inlineStr">
@@ -1302,15 +1381,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K7" s="38" t="n">
+      <c r="K7" s="73" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="74" t="n"/>
-      <c r="M7" s="72" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M7" s="44" t="n"/>
       <c r="N7" s="34" t="n"/>
       <c r="O7" s="34" t="n"/>
       <c r="P7" s="46" t="n"/>
@@ -1414,15 +1489,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K9" s="36" t="n">
+      <c r="K9" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="67" t="n"/>
-      <c r="M9" s="68" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L9" s="68" t="n"/>
+      <c r="M9" s="36" t="n"/>
       <c r="N9" s="34" t="n"/>
       <c r="O9" s="34" t="n"/>
       <c r="P9" s="46" t="n"/>
@@ -1526,15 +1597,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K11" s="36" t="n">
+      <c r="K11" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="67" t="n"/>
-      <c r="M11" s="68" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L11" s="68" t="n"/>
+      <c r="M11" s="36" t="n"/>
       <c r="N11" s="34" t="n"/>
       <c r="O11" s="34" t="n"/>
       <c r="P11" s="46" t="n"/>
@@ -1586,7 +1653,7 @@
       <c r="K12" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="73" t="n">
+      <c r="L12" s="72" t="n">
         <v>64</v>
       </c>
       <c r="M12" s="38" t="inlineStr">
@@ -1629,15 +1696,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K13" s="38" t="n">
+      <c r="K13" s="73" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="74" t="n"/>
-      <c r="M13" s="75" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M13" s="38" t="n"/>
       <c r="N13" s="34" t="n"/>
       <c r="O13" s="34" t="n"/>
       <c r="P13" s="46" t="n"/>
@@ -1688,7 +1751,7 @@
       <c r="K14" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="73" t="n">
+      <c r="L14" s="72" t="n">
         <v>100000</v>
       </c>
       <c r="M14" s="38" t="inlineStr">
@@ -1736,15 +1799,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K15" s="38" t="n">
+      <c r="K15" s="73" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="74" t="n"/>
-      <c r="M15" s="75" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M15" s="38" t="n"/>
       <c r="N15" s="34" t="n"/>
       <c r="O15" s="34" t="n"/>
       <c r="P15" s="46" t="n"/>
@@ -1772,13 +1831,13 @@
           <t>https://open.undp.org/projects/00085124</t>
         </is>
       </c>
-      <c r="D16" s="76" t="n">
+      <c r="D16" s="75" t="n">
         <v>128000</v>
       </c>
-      <c r="E16" s="77" t="n"/>
-      <c r="F16" s="77" t="n"/>
-      <c r="G16" s="77" t="n"/>
-      <c r="H16" s="76" t="inlineStr">
+      <c r="E16" s="76" t="n"/>
+      <c r="F16" s="76" t="n"/>
+      <c r="G16" s="76" t="n"/>
+      <c r="H16" s="75" t="inlineStr">
         <is>
           <t>Non-VF</t>
         </is>
@@ -1796,7 +1855,7 @@
       <c r="K16" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="73" t="n">
+      <c r="L16" s="72" t="n">
         <v>10</v>
       </c>
       <c r="M16" s="38" t="inlineStr">
@@ -1824,11 +1883,11 @@
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="36" t="n"/>
       <c r="C17" s="40" t="n"/>
-      <c r="D17" s="76" t="n"/>
-      <c r="E17" s="76" t="n"/>
-      <c r="F17" s="76" t="n"/>
-      <c r="G17" s="76" t="n"/>
-      <c r="H17" s="76" t="n"/>
+      <c r="D17" s="75" t="n"/>
+      <c r="E17" s="75" t="n"/>
+      <c r="F17" s="75" t="n"/>
+      <c r="G17" s="75" t="n"/>
+      <c r="H17" s="75" t="n"/>
       <c r="I17" s="36" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -1839,15 +1898,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K17" s="38" t="n">
+      <c r="K17" s="73" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="74" t="n"/>
-      <c r="M17" s="75" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M17" s="38" t="n"/>
       <c r="N17" s="34" t="n"/>
       <c r="O17" s="34" t="n"/>
       <c r="P17" s="46" t="n"/>
@@ -1861,7 +1916,7 @@
       <c r="X17" s="52" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="N2:N9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
@@ -1892,12 +1947,6 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
@@ -1906,6 +1955,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2072,20 +2122,20 @@
       </c>
     </row>
     <row r="3" ht="121.5" customHeight="1">
-      <c r="A3" s="78" t="n">
+      <c r="A3" s="77" t="n">
         <v>110578</v>
       </c>
-      <c r="B3" s="78" t="inlineStr">
+      <c r="B3" s="77" t="inlineStr">
         <is>
           <t>Resiliencia Energetica post Irma</t>
         </is>
       </c>
-      <c r="C3" s="79" t="inlineStr">
+      <c r="C3" s="78" t="inlineStr">
         <is>
           <t>http://open.undp.org/projects/00110578</t>
         </is>
       </c>
-      <c r="D3" s="78" t="n">
+      <c r="D3" s="77" t="n">
         <v>7710027</v>
       </c>
       <c r="E3" s="5" t="n"/>
@@ -2116,10 +2166,10 @@
       <c r="S3" s="23" t="n"/>
     </row>
     <row r="4" customFormat="1" s="23">
-      <c r="A4" s="80" t="n"/>
-      <c r="B4" s="80" t="n"/>
-      <c r="C4" s="80" t="n"/>
-      <c r="D4" s="80" t="n"/>
+      <c r="A4" s="79" t="n"/>
+      <c r="B4" s="79" t="n"/>
+      <c r="C4" s="79" t="n"/>
+      <c r="D4" s="79" t="n"/>
       <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -2944,288 +2994,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="81" t="inlineStr">
+      <c r="A1" s="80" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="81" t="inlineStr">
+      <c r="B1" s="80" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="82" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="82" t="inlineStr">
+      <c r="B2" s="81" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="82" t="inlineStr">
+      <c r="A3" s="81" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="82" t="inlineStr">
+      <c r="B3" s="81" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="82" t="inlineStr">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="82" t="inlineStr">
+      <c r="B4" s="81" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="82" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="82" t="inlineStr">
+      <c r="B5" s="81" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="82" t="inlineStr">
+      <c r="A6" s="81" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="82" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1">
-      <c r="A7" s="82" t="inlineStr">
+      <c r="A7" s="81" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="82" t="inlineStr">
+      <c r="B7" s="81" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="82" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="82" t="inlineStr">
+      <c r="B8" s="81" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1">
-      <c r="A9" s="82" t="inlineStr">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="82" t="inlineStr">
+      <c r="B9" s="81" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="82" t="inlineStr">
+      <c r="A10" s="81" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="82" t="inlineStr">
+      <c r="B10" s="81" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="82" t="inlineStr">
+      <c r="A11" s="81" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="82" t="inlineStr">
+      <c r="B11" s="81" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="82" t="inlineStr">
+      <c r="A12" s="81" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="82" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="82" t="inlineStr">
+      <c r="A13" s="81" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="82" t="inlineStr">
+      <c r="B13" s="81" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="82" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="82" t="inlineStr">
+      <c r="B14" s="81" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="82" t="inlineStr">
+      <c r="A15" s="81" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="82" t="inlineStr">
+      <c r="B15" s="81" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="82" t="inlineStr">
+      <c r="A16" s="81" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="82" t="inlineStr">
+      <c r="B16" s="81" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="82" t="inlineStr">
+      <c r="A17" s="81" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="82" t="inlineStr">
+      <c r="B17" s="81" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="82" t="inlineStr">
+      <c r="A18" s="81" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="82" t="inlineStr">
+      <c r="B18" s="81" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76.5" customHeight="1">
-      <c r="A19" s="82" t="inlineStr">
+      <c r="A19" s="81" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="82" t="inlineStr">
+      <c r="B19" s="81" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1">
-      <c r="A20" s="82" t="inlineStr">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="82" t="inlineStr">
+      <c r="B20" s="81" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45.75" customHeight="1">
-      <c r="A21" s="82" t="inlineStr">
+      <c r="A21" s="81" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="82" t="inlineStr">
+      <c r="B21" s="81" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="82" t="inlineStr">
+      <c r="A22" s="81" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="82" t="inlineStr">
+      <c r="B22" s="81" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="82" t="inlineStr">
+      <c r="A23" s="81" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="82" t="inlineStr">
+      <c r="B23" s="81" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="82" t="inlineStr">
+      <c r="A24" s="81" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="82" t="inlineStr">
+      <c r="B24" s="81" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
